--- a/Team-Data/2007-08/1-12-2007-08.xlsx
+++ b/Team-Data/2007-08/1-12-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -742,7 +809,7 @@
         <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
@@ -775,10 +842,10 @@
         <v>2</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>11</v>
@@ -787,7 +854,7 @@
         <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="n">
         <v>23</v>
@@ -799,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
@@ -811,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -843,67 +910,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.857</v>
+        <v>0.882</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
       <c r="J3" t="n">
-        <v>74.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O3" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P3" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0.767</v>
       </c>
       <c r="R3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S3" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="T3" t="n">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="U3" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V3" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
@@ -912,16 +979,16 @@
         <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>98.7</v>
+        <v>99.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>14</v>
       </c>
       <c r="AI3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -948,22 +1015,22 @@
         <v>9</v>
       </c>
       <c r="AM3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN3" t="n">
         <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
         <v>7</v>
@@ -975,25 +1042,25 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -1025,67 +1092,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
         <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P4" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.694</v>
+        <v>0.695</v>
       </c>
       <c r="R4" t="n">
         <v>10.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T4" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>5.5</v>
@@ -1094,16 +1161,16 @@
         <v>23.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB4" t="n">
-        <v>94.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1133,19 +1200,19 @@
         <v>17</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
         <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>23</v>
@@ -1157,16 +1224,16 @@
         <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
@@ -1175,7 +1242,7 @@
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1294,10 +1361,10 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1309,22 +1376,22 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP5" t="n">
         <v>25</v>
       </c>
-      <c r="AP5" t="n">
-        <v>26</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1339,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
         <v>15</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1491,13 +1558,13 @@
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
         <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1506,13 +1573,13 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
         <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>5</v>
@@ -1521,13 +1588,13 @@
         <v>27</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY6" t="n">
         <v>17</v>
@@ -1536,7 +1603,7 @@
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.703</v>
+        <v>0.694</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0.468</v>
@@ -1610,13 +1677,13 @@
         <v>26.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="R7" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
         <v>42.1</v>
@@ -1625,31 +1692,31 @@
         <v>20.5</v>
       </c>
       <c r="V7" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W7" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA7" t="n">
         <v>21.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -1661,13 +1728,13 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
         <v>5</v>
@@ -1691,16 +1758,16 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
         <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1724,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
@@ -1897,7 +1964,7 @@
         <v>16</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -1935,85 +2002,85 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.757</v>
+        <v>0.75</v>
       </c>
       <c r="H9" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>37.1</v>
       </c>
       <c r="J9" t="n">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.464</v>
+        <v>0.466</v>
       </c>
       <c r="L9" t="n">
         <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="O9" t="n">
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.769</v>
+        <v>0.764</v>
       </c>
       <c r="R9" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="S9" t="n">
         <v>29.5</v>
       </c>
       <c r="T9" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U9" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V9" t="n">
         <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
         <v>5.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
@@ -2040,28 +2107,28 @@
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
       </c>
       <c r="AP9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="n">
         <v>17</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
@@ -2070,13 +2137,13 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
         <v>10</v>
@@ -2085,7 +2152,7 @@
         <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -2377,22 +2444,22 @@
         <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ11" t="n">
         <v>13</v>
@@ -2428,10 +2495,10 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
         <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.447</v>
+        <v>0.432</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,37 +2566,37 @@
         <v>38.4</v>
       </c>
       <c r="J12" t="n">
-        <v>86.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="T12" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U12" t="n">
         <v>22.8</v>
@@ -2538,10 +2605,10 @@
         <v>16.2</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
@@ -2553,10 +2620,10 @@
         <v>21.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.1</v>
+        <v>102.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
@@ -2565,13 +2632,13 @@
         <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2586,13 +2653,13 @@
         <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
         <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -2607,7 +2674,7 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
@@ -2616,10 +2683,10 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,7 +2695,7 @@
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2730,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.303</v>
+        <v>0.313</v>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J13" t="n">
-        <v>79.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.424</v>
+        <v>0.422</v>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.332</v>
       </c>
       <c r="O13" t="n">
         <v>20.7</v>
@@ -2702,22 +2769,22 @@
         <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="S13" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T13" t="n">
-        <v>41.8</v>
+        <v>42.2</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W13" t="n">
         <v>6.7</v>
@@ -2726,22 +2793,22 @@
         <v>5.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z13" t="n">
         <v>21.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,25 +2820,25 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM13" t="n">
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>10</v>
@@ -2780,37 +2847,37 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
         <v>30</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2953,37 +3020,37 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
         <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3120,13 +3187,13 @@
         <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
         <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>6</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
@@ -3144,10 +3211,10 @@
         <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
@@ -3165,7 +3232,7 @@
         <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-6</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
@@ -3299,25 +3366,25 @@
         <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM16" t="n">
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>15</v>
@@ -3329,7 +3396,7 @@
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS16" t="n">
         <v>24</v>
@@ -3350,7 +3417,7 @@
         <v>15</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -3391,133 +3458,133 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.405</v>
+        <v>0.417</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.453</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M17" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.344</v>
+        <v>0.336</v>
       </c>
       <c r="O17" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P17" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="R17" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.3</v>
+        <v>94.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>26</v>
       </c>
       <c r="AP17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
@@ -3529,16 +3596,16 @@
         <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,10 +3658,10 @@
         <v>36.2</v>
       </c>
       <c r="J18" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
         <v>5.5</v>
@@ -3603,31 +3670,31 @@
         <v>16.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
         <v>14.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.721</v>
+        <v>0.717</v>
       </c>
       <c r="R18" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T18" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U18" t="n">
         <v>18.6</v>
       </c>
       <c r="V18" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="W18" t="n">
         <v>7.2</v>
@@ -3636,7 +3703,7 @@
         <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z18" t="n">
         <v>23.9</v>
@@ -3645,13 +3712,13 @@
         <v>17.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.6</v>
+        <v>-9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,25 +3730,25 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,25 +3757,25 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>-4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -3854,10 +3921,10 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM19" t="n">
         <v>16</v>
@@ -3875,13 +3942,13 @@
         <v>26</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
@@ -3896,7 +3963,7 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4033,7 +4100,7 @@
         <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>18</v>
@@ -4066,13 +4133,13 @@
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
@@ -4081,7 +4148,7 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>27</v>
@@ -4209,7 +4276,7 @@
         <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4227,13 +4294,13 @@
         <v>18</v>
       </c>
       <c r="AN21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>14</v>
       </c>
       <c r="AP21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>28</v>
@@ -4245,7 +4312,7 @@
         <v>28</v>
       </c>
       <c r="AT21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
         <v>17</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
         <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.59</v>
+        <v>0.605</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4319,43 +4386,43 @@
         <v>36.8</v>
       </c>
       <c r="J22" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.463</v>
       </c>
       <c r="L22" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="O22" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S22" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T22" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V22" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W22" t="n">
         <v>6.4</v>
@@ -4367,22 +4434,22 @@
         <v>4.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF22" t="n">
         <v>10</v>
@@ -4394,10 +4461,10 @@
         <v>5</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>7</v>
@@ -4412,13 +4479,13 @@
         <v>13</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
         <v>27</v>
@@ -4430,13 +4497,13 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,7 +4512,7 @@
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
         <v>23</v>
@@ -4579,13 +4646,13 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK23" t="n">
         <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
         <v>28</v>
@@ -4594,10 +4661,10 @@
         <v>29</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ23" t="n">
         <v>27</v>
@@ -4612,7 +4679,7 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV23" t="n">
         <v>23</v>
@@ -4621,7 +4688,7 @@
         <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>19</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -4665,85 +4732,85 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>0.703</v>
+        <v>0.694</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="J24" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.49</v>
+        <v>0.488</v>
       </c>
       <c r="L24" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O24" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P24" t="n">
         <v>22.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R24" t="n">
         <v>8.9</v>
       </c>
       <c r="S24" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U24" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="V24" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W24" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.3</v>
+        <v>110</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4755,7 +4822,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4764,25 +4831,25 @@
         <v>4</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>3</v>
       </c>
       <c r="AM24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN24" t="n">
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
         <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,25 +4867,25 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4937,13 +5004,13 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI25" t="n">
         <v>19</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4958,7 +5025,7 @@
         <v>2</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
         <v>21</v>
@@ -4967,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
@@ -4979,7 +5046,7 @@
         <v>12</v>
       </c>
       <c r="AV25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW25" t="n">
         <v>29</v>
@@ -4988,7 +5055,7 @@
         <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
         <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5047,19 +5114,19 @@
         <v>35.5</v>
       </c>
       <c r="J26" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M26" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O26" t="n">
         <v>21.6</v>
@@ -5068,13 +5135,13 @@
         <v>27.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.796</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S26" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T26" t="n">
         <v>39.6</v>
@@ -5083,7 +5150,7 @@
         <v>17.9</v>
       </c>
       <c r="V26" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
@@ -5092,31 +5159,31 @@
         <v>3.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA26" t="n">
         <v>23.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
         <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
@@ -5134,13 +5201,13 @@
         <v>19</v>
       </c>
       <c r="AM26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP26" t="n">
         <v>8</v>
@@ -5149,10 +5216,10 @@
         <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5161,16 +5228,16 @@
         <v>29</v>
       </c>
       <c r="AV26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW26" t="n">
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
@@ -5229,76 +5296,76 @@
         <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L27" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
         <v>20.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.389</v>
+        <v>0.385</v>
       </c>
       <c r="O27" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.753</v>
+        <v>0.758</v>
       </c>
       <c r="R27" t="n">
         <v>10.2</v>
       </c>
       <c r="S27" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="T27" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U27" t="n">
         <v>22.1</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y27" t="n">
         <v>4.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="n">
         <v>22</v>
@@ -5310,7 +5377,7 @@
         <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>5</v>
@@ -5322,19 +5389,19 @@
         <v>3</v>
       </c>
       <c r="AO27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR27" t="n">
         <v>24</v>
       </c>
-      <c r="AP27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>23</v>
-      </c>
       <c r="AS27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT27" t="n">
         <v>20</v>
@@ -5343,13 +5410,13 @@
         <v>9</v>
       </c>
       <c r="AV27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
         <v>15</v>
@@ -5358,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5486,7 +5553,7 @@
         <v>18</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>6</v>
@@ -5495,22 +5562,22 @@
         <v>27</v>
       </c>
       <c r="AL28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM28" t="n">
         <v>27</v>
       </c>
       <c r="AN28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>13</v>
@@ -5525,13 +5592,13 @@
         <v>20</v>
       </c>
       <c r="AV28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW28" t="n">
         <v>22</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5668,7 +5735,7 @@
         <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>10</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
@@ -5710,10 +5777,10 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX29" t="n">
         <v>23</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>24</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
         <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>0.553</v>
+        <v>0.541</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,10 +5842,10 @@
         <v>39.6</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
       <c r="L30" t="n">
         <v>3.9</v>
@@ -5787,34 +5854,34 @@
         <v>11.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O30" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="P30" t="n">
-        <v>29.3</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.749</v>
+        <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T30" t="n">
         <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="V30" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
@@ -5823,13 +5890,13 @@
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.1</v>
+        <v>104.8</v>
       </c>
       <c r="AC30" t="n">
         <v>4.7</v>
@@ -5838,7 +5905,7 @@
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -5847,7 +5914,7 @@
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
@@ -5856,10 +5923,10 @@
         <v>14</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM30" t="n">
         <v>30</v>
@@ -5868,19 +5935,19 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP30" t="n">
         <v>5</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5892,10 +5959,10 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
@@ -5939,115 +6006,115 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>0.543</v>
+        <v>0.529</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L31" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.342</v>
+        <v>0.348</v>
       </c>
       <c r="O31" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="P31" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.797</v>
+        <v>0.793</v>
       </c>
       <c r="R31" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T31" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U31" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="V31" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="X31" t="n">
         <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
         <v>19.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG31" t="n">
         <v>14</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13</v>
       </c>
       <c r="AH31" t="n">
         <v>6</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM31" t="n">
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6059,7 +6126,7 @@
         <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
         <v>14</v>
@@ -6068,19 +6135,19 @@
         <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-12-2007-08</t>
+          <t>2008-01-12</t>
         </is>
       </c>
     </row>
